--- a/excel/universities/university-of-vaasa.xlsx
+++ b/excel/universities/university-of-vaasa.xlsx
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.uwasa.fi/en/education/applying</t>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/masters-programmes/how-apply</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -125,7 +125,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">English-language master's programmes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -140,12 +140,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Programme-specific</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill program-specific information here</t>
+          <t xml:space="preserve">University of Vaasa offers both joint application and rolling admission routes for autumn 2026 depending on applicant background and programme.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -161,7 +161,7 @@
 
 <file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -229,7 +229,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Joint application round</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -239,12 +239,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -254,15 +254,67 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.uwasa.fi/en/education/applying</t>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/masters-programmes/how-apply</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify annual deadlines</t>
+          <t xml:space="preserve">Rolling admission is also available for eligible applicants from 2025-10-01 until 2026-03-31.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling admission</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-01</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-31</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/masters-programmes/how-apply</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling admission is open only to applicants with previous degrees from non-Finnish higher education institutions.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -275,7 +327,7 @@
 
 <file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -333,30 +385,198 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Joint application round</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport</t>
+          <t xml:space="preserve">Degree certificate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High-quality scan of original degree certificate is required.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/international-masters-programmes/application-process</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joint application round</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.uwasa.fi/en/education/applying</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grading system explanation is mandatory if not clearly stated in the transcript.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/international-masters-programmes/application-process</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joint application round</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official translations</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If needed</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required for degree certificate and transcript if documents are not in English Finnish or Swedish.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/international-masters-programmes/application-process</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joint application round</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language proficiency</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted according to programme admissions criteria.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/international-masters-programmes/application-process</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joint application round</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Passport or official ID</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residence permit card copy also needed if applying for tuition fee exemption based on permit status.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/international-masters-programmes/application-process</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -369,7 +589,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -420,15 +640,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">official_profile_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">email</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -437,7 +672,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Vaasa</t>
+          <t xml:space="preserve">University Name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,7 +692,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Area 1; Research Area 2</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -482,7 +717,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.uwasa.fi/en</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -492,7 +727,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-14</t>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>

--- a/excel/universities/university-of-vaasa.xlsx
+++ b/excel/universities/university-of-vaasa.xlsx
@@ -589,7 +589,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,17 +672,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">University Name</t>
+          <t xml:space="preserve">University of Vaasa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department Name</t>
+          <t xml:space="preserve">School of Technology and Innovations</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor Name</t>
+          <t xml:space="preserve">Tero Vartiainen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Information systems; Digital transformation; Human-computer interaction; Organizational communication</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">University of Vaasa official profile</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.uwasa.fi/en/person/tero-vartiainen</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -742,7 +742,84 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">University of Vaasa official profile used for title and research description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Management</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Harri Jalonen</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Knowledge management; Artificial intelligence in organizations; Social robotics; Futures studies</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa official profile</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/person/harri-jalonen</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa official profile used for title and research description.</t>
         </is>
       </c>
     </row>

--- a/excel/universities/university-of-vaasa.xlsx
+++ b/excel/universities/university-of-vaasa.xlsx
@@ -20,7 +20,8 @@
     <sheet name="UniversityInfo" sheetId="1" r:id="rId1"/>
     <sheet name="Deadlines" sheetId="2" r:id="rId2"/>
     <sheet name="Documents" sheetId="3" r:id="rId3"/>
-    <sheet name="Professors" sheetId="4" r:id="rId4"/>
+    <sheet name="Departments" sheetId="4" r:id="rId4"/>
+    <sheet name="Professors" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -589,6 +590,251 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">university_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parent_unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campus_or_city</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus_areas</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">official_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaasa</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accounting; Finance</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/about/organization</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organization page.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Management</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaasa</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Management; Public management</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/about/organization</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organization page.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Marketing and Communication</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaasa</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marketing; Communication</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/about/organization</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organization page.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Technology and Innovations</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaasa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technology; Information systems; Industrial management</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/about/organization</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organization page.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
